--- a/CUSTOMER FFU CHART/FABRIC_CUSTOMERFFUCHART_fv.xlsx
+++ b/CUSTOMER FFU CHART/FABRIC_CUSTOMERFFUCHART_fv.xlsx
@@ -4628,8 +4628,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -4650,6 +4650,8 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:i0f84bba906045b4af568ee102a52dcb" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4709,6 +4711,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="96d24a6b-8465-4498-bb54-acea15c87a74" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -4748,6 +4755,13 @@
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="i0f84bba906045b4af568ee102a52dcb" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="i0f84bba906045b4af568ee102a52dcb" ma:taxonomyFieldName="RevIMBCS" ma:displayName="Retention Policy" ma:indexed="true" ma:default="5;#Daily Work Documents [Standard]|c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b" ma:fieldId="{20f84bba-9060-45b4-af56-8ee102a52dcb}" ma:sspId="c81b625c-6132-4315-8b99-2d7d4df07560" ma:termSetId="1d8deb5c-7ccc-4e04-a1de-f52ad8333138" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -4865,13 +4879,23 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="57147975-5687-4135-8263-39f5df548c17">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74" xsi:nil="true"/>
+    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Value>5</Value>
+    </TaxCatchAll>
+    <i0f84bba906045b4af568ee102a52dcb xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Daily Work Documents [Standard]</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b</TermId>
+        </TermInfo>
+      </Terms>
+    </i0f84bba906045b4af568ee102a52dcb>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3F8CD2-BD3B-4458-9F63-DCF61048EB64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CB79BA0-3C4C-4C52-8526-82B028253881}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
